--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/IOWA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/IOWA_2011.xlsx
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C104">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C405">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C603">
